--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-22T14:03:50+00:00</t>
+    <t>2024-09-22T15:24:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-22T15:24:30+00:00</t>
+    <t>2024-09-22T15:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-22T15:59:26+00:00</t>
+    <t>2024-09-23T04:30:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-23T04:30:00+00:00</t>
+    <t>2024-09-23T07:09:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-23T07:09:18+00:00</t>
+    <t>2024-09-23T10:28:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-23T10:28:49+00:00</t>
+    <t>2024-09-23T15:26:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-23T15:26:21+00:00</t>
+    <t>2024-09-24T04:28:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-24T04:28:49+00:00</t>
+    <t>2024-09-24T10:26:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-24T10:26:06+00:00</t>
+    <t>2024-09-24T15:26:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-24T15:26:24+00:00</t>
+    <t>2024-09-25T04:31:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T04:31:00+00:00</t>
+    <t>2024-09-25T10:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T10:28:43+00:00</t>
+    <t>2024-09-25T15:26:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T15:26:24+00:00</t>
+    <t>2024-09-26T04:29:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-26T04:29:27+00:00</t>
+    <t>2024-09-26T10:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-26T10:26:31+00:00</t>
+    <t>2024-09-26T15:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-26T15:26:51+00:00</t>
+    <t>2024-09-27T04:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T04:29:37+00:00</t>
+    <t>2024-09-27T10:26:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T10:26:36+00:00</t>
+    <t>2024-09-27T15:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T15:26:04+00:00</t>
+    <t>2024-09-28T04:28:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-28T04:28:07+00:00</t>
+    <t>2024-09-28T10:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-28T10:24:26+00:00</t>
+    <t>2024-09-28T15:28:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-28T15:28:01+00:00</t>
+    <t>2024-09-29T04:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-29T04:28:16+00:00</t>
+    <t>2024-09-29T10:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-29T10:26:20+00:00</t>
+    <t>2024-09-29T15:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-29T15:26:12+00:00</t>
+    <t>2024-09-30T04:29:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-30T04:29:35+00:00</t>
+    <t>2024-09-30T10:28:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-30T10:28:53+00:00</t>
+    <t>2024-09-30T15:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-30T15:28:34+00:00</t>
+    <t>2024-10-01T04:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-01T04:31:24+00:00</t>
+    <t>2024-10-01T10:28:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-01T10:28:08+00:00</t>
+    <t>2024-10-01T15:26:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-01T15:26:35+00:00</t>
+    <t>2024-10-02T04:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T04:28:59+00:00</t>
+    <t>2024-10-02T10:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T10:26:19+00:00</t>
+    <t>2024-10-02T15:26:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T15:26:35+00:00</t>
+    <t>2024-10-03T04:30:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-03T04:30:54+00:00</t>
+    <t>2024-10-03T10:26:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-03T10:26:23+00:00</t>
+    <t>2024-10-03T15:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-03T15:26:39+00:00</t>
+    <t>2024-10-04T04:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-04T04:28:33+00:00</t>
+    <t>2024-10-04T10:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-04T10:27:54+00:00</t>
+    <t>2024-10-04T15:27:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-04T15:27:36+00:00</t>
+    <t>2024-10-05T04:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-05T04:30:22+00:00</t>
+    <t>2024-10-05T09:14:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-05T09:14:36+00:00</t>
+    <t>2024-10-05T10:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-05T10:26:19+00:00</t>
+    <t>2024-10-05T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-05T15:26:02+00:00</t>
+    <t>2024-10-06T04:30:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-06T04:30:38+00:00</t>
+    <t>2024-10-06T10:25:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-06T10:25:36+00:00</t>
+    <t>2024-10-06T15:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-06T15:25:29+00:00</t>
+    <t>2024-10-07T04:29:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-07T04:29:05+00:00</t>
+    <t>2024-10-07T10:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-07T10:29:06+00:00</t>
+    <t>2024-10-07T15:26:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-07T15:26:36+00:00</t>
+    <t>2024-10-08T04:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-08T04:28:37+00:00</t>
+    <t>2024-10-08T10:27:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-08T10:27:36+00:00</t>
+    <t>2024-10-08T15:27:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-08T15:27:10+00:00</t>
+    <t>2024-10-09T04:28:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-09T04:28:48+00:00</t>
+    <t>2024-10-09T10:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-09T10:27:53+00:00</t>
+    <t>2024-10-09T15:27:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-09T15:27:11+00:00</t>
+    <t>2024-10-10T04:28:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-10T04:28:45+00:00</t>
+    <t>2024-10-10T10:28:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-10T10:28:20+00:00</t>
+    <t>2024-10-10T15:26:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-10T15:26:09+00:00</t>
+    <t>2024-10-11T04:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T04:30:22+00:00</t>
+    <t>2024-10-11T10:25:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T10:25:17+00:00</t>
+    <t>2024-10-11T15:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T15:26:07+00:00</t>
+    <t>2024-10-12T04:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-12T04:29:12+00:00</t>
+    <t>2024-10-12T10:25:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-12T10:25:49+00:00</t>
+    <t>2024-10-12T15:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-12T15:25:31+00:00</t>
+    <t>2024-10-13T04:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T04:29:58+00:00</t>
+    <t>2024-10-13T10:26:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T10:26:05+00:00</t>
+    <t>2024-10-13T15:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T15:31:06+00:00</t>
+    <t>2024-10-13T16:24:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T16:24:50+00:00</t>
+    <t>2024-10-14T04:28:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T04:28:54+00:00</t>
+    <t>2024-10-14T11:37:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T11:37:57+00:00</t>
+    <t>2024-10-14T15:26:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T15:26:29+00:00</t>
+    <t>2024-10-15T04:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T04:28:43+00:00</t>
+    <t>2024-10-15T09:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T09:44:23+00:00</t>
+    <t>2024-10-15T10:29:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T10:29:21+00:00</t>
+    <t>2024-10-15T15:26:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T15:26:25+00:00</t>
+    <t>2024-10-16T04:28:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T04:28:57+00:00</t>
+    <t>2024-10-16T10:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T10:25:25+00:00</t>
+    <t>2024-10-16T12:37:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T12:37:09+00:00</t>
+    <t>2024-10-17T04:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T04:29:22+00:00</t>
+    <t>2024-10-17T10:28:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T10:28:31+00:00</t>
+    <t>2024-10-17T15:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T15:25:42+00:00</t>
+    <t>2024-10-18T04:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T04:29:52+00:00</t>
+    <t>2024-10-18T07:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T07:07:45+00:00</t>
+    <t>2024-10-18T10:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T10:29:00+00:00</t>
+    <t>2024-10-18T15:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T15:28:09+00:00</t>
+    <t>2024-10-19T04:28:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-19T04:28:49+00:00</t>
+    <t>2024-10-19T10:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-19T10:25:11+00:00</t>
+    <t>2024-10-19T15:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-19T15:24:42+00:00</t>
+    <t>2024-10-20T04:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T04:28:58+00:00</t>
+    <t>2024-10-20T10:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T10:26:58+00:00</t>
+    <t>2024-10-20T15:25:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T15:25:43+00:00</t>
+    <t>2024-10-21T04:29:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T04:29:35+00:00</t>
+    <t>2024-10-21T10:29:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
+++ b/ig/main/ASS-A32-StatutMotifPersonnePriseCharge.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T10:29:31+00:00</t>
+    <t>2024-10-21T15:27:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
